--- a/output/pdf_financials_xlsx/ORE.xlsx
+++ b/output/pdf_financials_xlsx/ORE.xlsx
@@ -6328,7 +6328,7 @@
         <v>483.211</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>1.730892</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -6391,46 +6391,46 @@
         <v>3.918566</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>7.019751</v>
+        <v>10.631625</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.305551</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.490331</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>12.79622</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.3785</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.883352</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>16.93144</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>18.270665</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>19.838222</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>29.162636</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>30.658</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>31.236</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>32.066</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>32.708</v>
       </c>
     </row>
     <row r="93">
@@ -11450,7 +11450,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -13774,7 +13778,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -18122,7 +18130,11 @@
           <t>Reserves 18,270,665</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -20936,7 +20948,11 @@
           <t>Foreign currency translation reserve 972,461</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ORE.xlsx
+++ b/output/pdf_financials_xlsx/ORE.xlsx
@@ -1002,10 +1002,10 @@
         <v>9.704369</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>15.787568</v>
+        <v>15.795533</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>23.008223</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>0</v>
@@ -1073,10 +1073,10 @@
         <v>-9.704369</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-15.787568</v>
+        <v>-15.795533</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-23.008223</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-8.585063</v>
@@ -2608,34 +2608,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.371366</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.538551</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.538551</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>28.698108</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>16.833596</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.476471</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.415283</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.835256</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>22.099768</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.148801</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>31.453567</v>
@@ -2644,19 +2644,19 @@
         <v>11.855497</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>36.08298</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>19.483</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>74.021</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>97.952</v>
       </c>
     </row>
     <row r="35">
@@ -2734,34 +2734,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.371366</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.538551</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.538551</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>28.698108</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>16.833596</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>9.476471</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.415283</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.835256</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>22.099768</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.897075</v>
+        <v>12.045876</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>31.770236</v>
@@ -2770,19 +2770,19 @@
         <v>12.37171</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>36.08298</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>19.483</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>74.021</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>97.952</v>
       </c>
     </row>
     <row r="37">
@@ -3490,34 +3490,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.839451</v>
+        <v>0.468085</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.920629</v>
+        <v>0.382078</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>29.446646</v>
+        <v>0.748538</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17.438747</v>
+        <v>0.605151</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>9.643834</v>
+        <v>0.167363</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.543871</v>
+        <v>0.128588</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.942735</v>
+        <v>0.107479</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>22.208066</v>
+        <v>0.108298</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>21.310991</v>
+        <v>10.16219</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.405246</v>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.056802</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.056802</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -36370,7 +36370,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -62206,7 +62210,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">

--- a/output/pdf_financials_xlsx/ORE.xlsx
+++ b/output/pdf_financials_xlsx/ORE.xlsx
@@ -1460,7 +1460,7 @@
         <v>-0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0.956</v>
+        <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>13.23</v>
@@ -1717,13 +1717,13 @@
         <v>-18.721131</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.93</v>
+        <v>1.886</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>43.146</v>
+        <v>49.623</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>55.711</v>
+        <v>64.084</v>
       </c>
       <c r="S20" s="1" t="inlineStr">
         <is>
@@ -1906,13 +1906,13 @@
         <v>-18.721131</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.93</v>
+        <v>1.886</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>43.146</v>
+        <v>49.623</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>55.711</v>
+        <v>64.084</v>
       </c>
       <c r="S23" s="1" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>50.68928950159067</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>21.04911460073505</v>
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2.141327623126338</v>
+        <v>4.342520319587392</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>15.8922395217521</v>
+        <v>18.27795396532482</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>19.64996807951551</v>
+        <v>22.60323014140246</v>
       </c>
       <c r="S32" s="1" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.010388</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="3" t="n">
-        <v>0</v>
+        <v>-13.19</v>
       </c>
     </row>
     <row r="127">
@@ -27198,7 +27198,11 @@
           <t>Dividends paid to non-controlling interests 17</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -48390,7 +48394,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -55232,11 +55240,7 @@
           <t>Shareholders</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
